--- a/out/GC-017_比选台账_V1原始.xlsx
+++ b/out/GC-017_比选台账_V1原始.xlsx
@@ -759,7 +759,11 @@
       <c r="H9" s="9" t="n">
         <v>5622</v>
       </c>
-      <c r="I9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>乙：未税单价500.00根超参考区间上限102约4.9倍（异常线索，仅提示不自动改写，规则第五条）</t>
+        </is>
+      </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
           <t>甲：甲方报价.xlsx · 工作表「甲方含税报价」第9行；乙：乙方报价.pdf · 第1页第9行；丙：报价扫描-1.png · 条目C08；丁：丁方报价截图-1.png · 条目C08</t>
@@ -1136,7 +1140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1600,22 +1604,22 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>乙</t>
+          <t>甲</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>资质</t>
+          <t>税率</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>检测资质摘要待补充</t>
+          <t>发票类型未说明（专票可抵扣则比价看未税，普票含税即真实成本）</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>补充/续期资质材料</t>
+          <t>发票类型说明（专票/普票）</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -1625,7 +1629,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>资格材料登记.xlsx；系统只整理缺件与疑点，有效性由评审人员判断</t>
+          <t>税率已声明；发票类型未说明，双口径并排供商务判断</t>
         </is>
       </c>
     </row>
@@ -1637,30 +1641,178 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
+          <t>乙</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>税率</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>发票类型未说明（专票可抵扣则比价看未税，普票含税即真实成本）</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>发票类型说明（专票/普票）</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>税率已声明；发票类型未说明，双口径并排供商务判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>QB-014</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>丙</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>税率</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>发票类型未说明（专票可抵扣则比价看未税，普票含税即真实成本）</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>发票类型说明（专票/普票）</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>税率已声明；发票类型未说明，双口径并排供商务判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>QB-015</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
           <t>丁</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>税率</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>发票类型未说明（专票可抵扣则比价看未税，普票含税即真实成本）</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>发票类型说明（专票/普票）</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>税率已声明；发票类型未说明，双口径并排供商务判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>QB-016</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>乙</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>资质</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>检测资质摘要待补充</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>补充/续期资质材料</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>资格材料登记.xlsx；系统只整理缺件与疑点，有效性由评审人员判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>QB-017</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>丁</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>资质</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>资质2026-08-31到期，续期材料未提供</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>补充/续期资质材料</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>待补充</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>资格材料登记.xlsx；系统只整理缺件与疑点，有效性由评审人员判断</t>
         </is>
